--- a/AAII_Financials/Quarterly/GIS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GIS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>GIS</t>
   </si>
@@ -656,531 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46264</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="F7" s="2">
         <v>46075</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45984</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45893</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45802</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45711</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45620</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45529</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45438</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45347</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45256</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45165</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45074</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44983</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44892</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44801</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44710</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44619</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44528</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44437</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44346</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44164</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44073</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43982</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43884</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43793</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43702</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43611</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43520</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43429</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43338</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43156</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43065</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42974</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42883</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42792</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42701</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4389500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4609600</v>
+      </c>
+      <c r="F8" s="3">
         <v>4436700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4860800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4517500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4556200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4842200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5240100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4848100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4713900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5099200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5139400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4904700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>5030000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5125900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>5220700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4717600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4891200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4537700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>5024000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4539900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>4523600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4520000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>4719400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4364000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>5023000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4180300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>4420800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4002500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>4161700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4198300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>4411200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>4094000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>3890200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>3882300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>4198700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>3769200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>3806600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>3793200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>4112100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2898800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3000100</v>
+      </c>
+      <c r="F9" s="3">
         <v>3061400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3165300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2982700</v>
       </c>
-      <c r="G9" s="3">
-        <v>3073900</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>3073500</v>
+      </c>
+      <c r="J9" s="3">
         <v>3202900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3308800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3158500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3024600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3391200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3364900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3124800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3296500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3460400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3515100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3269200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3120800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3131800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3392400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2942300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2940100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2965400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2997800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2773100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3253000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2770100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2839400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2606900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2690800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>2755100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>2901500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>2696800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>2466700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>2622700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>2747700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>2442400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>2480700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>2457600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>2568700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1490700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1609500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1375300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1695500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1534800</v>
       </c>
-      <c r="G10" s="3">
-        <v>1482300</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>1482700</v>
+      </c>
+      <c r="J10" s="3">
         <v>1639300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1931300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1689600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1689300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1708000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1774500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1779900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1733500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1665500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1705600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1448400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1770400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1405900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1631600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1597600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1583500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1554600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1721600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1590900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1770000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1410200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1581400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1395600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1470900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1443200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1397200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1423500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1259600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1451000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1326800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1325900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>1335600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>1543400</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,52 +1248,54 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>256000</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
-        <v>256600</v>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>256600</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
-        <v>257800</v>
+      <c r="K12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
+      <c r="M12" s="3">
+        <v>257800</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
-        <v>257600</v>
+      <c r="O12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
+      <c r="Q12" s="3">
+        <v>257600</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
@@ -1341,8 +1369,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1460,175 +1494,187 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2823500</v>
+      </c>
+      <c r="F14" s="3">
         <v>37800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>125100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-1036100</v>
       </c>
-      <c r="G14" s="3">
-        <v>97900</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>98300</v>
+      </c>
+      <c r="J14" s="3">
         <v>-96500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>126000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>6400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>132200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>10600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>48300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-5500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-448600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-65900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-175000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>16100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-10700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>179300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>-32800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>-17500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>-15900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>79600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>195200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>40800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>194800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>-25000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>-14400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>-1800</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>23300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AP14" s="3">
         <v>105500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AQ14" s="3">
         <v>66400</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>139800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>139100</v>
+      </c>
+      <c r="F15" s="3">
         <v>139400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>138000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>138700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>135600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>134300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>129500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>139600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>140500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>146400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>128600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>137200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>135600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>137100</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1698,8 +1744,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,246 +1790,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3720400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3866500</v>
+      </c>
+      <c r="F17" s="3">
         <v>3859000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3992000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3812700</v>
       </c>
-      <c r="G17" s="3">
-        <v>3941500</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>3941100</v>
+      </c>
+      <c r="J17" s="3">
         <v>4033400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4147000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3999700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3788600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4163500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4175300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3947100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4139700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4385000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4399200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3610300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3846100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3695300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4196200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3666000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3942400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3660000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3769900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3477000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>4171400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3499200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3579400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3309900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3421000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>3525600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>3843200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>3471600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>3363200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>3273700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>3468900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>3143400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>3197400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>3250700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>3343200</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>669100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>743100</v>
+      </c>
+      <c r="F18" s="3">
         <v>577700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>868800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>704800</v>
       </c>
-      <c r="G18" s="3">
-        <v>614700</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>615100</v>
+      </c>
+      <c r="J18" s="3">
         <v>808800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1093100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>848400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>925300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>935700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>964100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>957600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>890300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>740900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>821500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1107300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1045100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>842400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>827800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>873900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>581200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>860000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>949500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>887000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>851600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>681100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>841400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>692600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>740700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>672700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>568000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>622400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>527000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>608600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>729800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>625800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>609200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>542500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>768900</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,294 +2085,308 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F20" s="3">
         <v>6100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>59600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-6800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-14400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-30000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-19200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-19100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-18000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-24200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-23500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-23400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-91500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-87700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-104500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-86500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-92700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-95900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-102600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-106000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-100600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-111100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-118600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-109800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-119400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-118700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-124800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-130800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-132700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-133500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-103100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-105200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-74900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-72400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-69300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>-76400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>-75500</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>827800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>864600</v>
+      </c>
+      <c r="F21" s="3">
         <v>711000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>947200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>850300</v>
       </c>
-      <c r="G21" s="3">
-        <v>744300</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>744700</v>
+      </c>
+      <c r="J21" s="3">
         <v>957500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1252600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1007200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1084900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1100100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1116900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1118300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1049300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>890700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>869600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1153900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1080300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>899600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>876200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>923800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>625400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>913400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>997900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>922000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>871300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>720000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>875600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>728000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>771400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>696400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>590200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>644100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>608000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>647300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>800600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>698500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>695200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>613300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>842000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>142200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>182500</v>
+      </c>
+      <c r="F22" s="3">
         <v>128400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>125900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>132800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>164300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>136300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>124600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>123600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>141500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>121700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>117800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>117000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>118600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>98300</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -2376,246 +2456,264 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>520900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2249500</v>
+      </c>
+      <c r="F23" s="3">
         <v>405400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>558200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1614900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>371100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>783400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>997100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>741000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>695700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>825600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>738300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>853500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>760800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>666200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>730000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1019600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>940600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>755900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>735100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>778000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>478600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>754000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>848900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>775900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>733000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>571300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>722000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>573900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>615900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>541900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>435300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>488900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>423900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>503400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>654900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>553400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>539900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>466100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-240400</v>
+      </c>
+      <c r="F24" s="3">
         <v>99900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>143900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>410900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>69100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>152400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>194800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>157400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>136000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>149300</v>
       </c>
       <c r="M24" s="3">
         <v>136000</v>
       </c>
       <c r="N24" s="3">
+        <v>149300</v>
+      </c>
+      <c r="O24" s="3">
+        <v>136000</v>
+      </c>
+      <c r="P24" s="3">
         <v>173200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>140700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>108300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>147100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>216100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>134500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>123200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>159700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>168900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>106900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>162000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>189400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>170800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>139600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>118200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>155500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>67200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>54700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>103000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>106600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>110700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>86400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>91000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>234900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>168500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>144200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>107000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2733,246 +2831,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>398100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2009100</v>
+      </c>
+      <c r="F26" s="3">
         <v>305500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>414300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1204000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>302000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>631000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>802300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>583600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>559700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>676300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>602300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>680300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>620100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>557900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>582900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>803500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>806100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>632700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>575400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>609100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>371700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>592000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>659500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>605100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>593400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>453100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>566500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>506700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>561200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>438900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>328700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>378200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>337500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>412400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>420000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>384900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>395700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>359100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>466000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2007900</v>
+      </c>
+      <c r="F27" s="3">
         <v>303100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>413000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1204200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>283500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>625600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>795700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>579900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>557500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>670100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>595500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>673500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>614900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>553100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>605900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>820000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>822800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>660300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>597200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>627000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>416800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>595700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>688400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>638900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>625700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>454100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>580800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>520600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>570200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>439600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>343400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>392300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>354400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>417900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>430500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>404700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>408900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>357800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>481800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3090,8 +3206,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3161,11 +3283,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3176,29 +3298,29 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>7200</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>523500</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3209,8 +3331,14 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3456,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,246 +3581,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-6100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-59600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>6800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>14400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>30000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>19200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>19100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>18000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>24200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>23500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>23400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>12700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>91500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>87700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>104500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>86500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>92700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>95900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>102600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>106000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>100600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>111100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>118600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>109800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>119400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>118700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>124800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>130800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>132700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>133500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>103100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>105200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>74900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>72400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>69300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>76400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2007900</v>
+      </c>
+      <c r="F33" s="3">
         <v>303100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>413000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1204200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>294000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>625600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>795700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>579900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>557500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>670100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>595500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>673500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>614900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>553100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>605900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>820000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>822800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>660300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>597200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>627000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>416800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>595700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>688400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>638900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>625700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>454100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>580800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>520600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>570200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>446800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>343400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>392300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>354400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>941400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>430500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>404700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>408900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>357800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>481800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,251 +3956,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2007900</v>
+      </c>
+      <c r="F35" s="3">
         <v>303100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>413000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1204200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>294000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>625600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>795700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>579900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>557500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>670100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>595500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>673500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>614900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>553100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>605900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>820000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>822800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>660300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>597200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>627000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>416800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>595700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>688400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>638900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>625700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>454100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>580800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>520600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>570200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>446800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>343400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>392300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>354400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>941400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>430500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>404700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>408900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>357800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>481800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46264</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="F38" s="2">
         <v>46075</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45984</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45893</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45802</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45711</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45620</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45529</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45438</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45347</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45256</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45165</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45074</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44983</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44892</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44801</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44710</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44619</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44528</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44437</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44346</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44164</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44073</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43982</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43884</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43793</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43702</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43611</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43520</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43429</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43338</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43156</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43065</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42974</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42883</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42792</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42701</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4260,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,127 +4305,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>433100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>453800</v>
+      </c>
+      <c r="F41" s="3">
         <v>785500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>683400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>952900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>363900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>521300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2292800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>468100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>418000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>588600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>593800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>490900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>585500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>618700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>644100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>594400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>569400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>844400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1021000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>710600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1505200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2754200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2582800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1796700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1677800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>606900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>560200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>504800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>450000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>547100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>532700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>432900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>399000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>953100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>962100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>820800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>766100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>899100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>809700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4291,14 +4471,14 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>117200</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4371,531 +4551,561 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1775200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1857100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1892600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1804300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1937100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1791000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1781900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1843800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1917800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1771100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1758800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1791100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1968900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1770200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1834000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1730400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1692100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1750400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1766100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1691700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1638500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1776200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1784300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1633000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1615100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1731100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1772700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1710500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1679700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1704100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1716800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>1709100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>1684200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>1496500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>1510500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>1546500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>1430100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>1427500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>1382700</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2163200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1917900</v>
+      </c>
+      <c r="F44" s="3">
         <v>1755700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2051500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2051500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1910800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1811600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1967900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1996400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1898200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1828000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2166000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2228800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>2172000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2083300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2121300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2089900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1867300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1710000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1797300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1935200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1820500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1758800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1712500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1605100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1426300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1542100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1719500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1700100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1559300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1544500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>1639200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>1685500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>1642200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>1452500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>1516500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>1595200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>1483600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>1461000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>1525500</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+      <c r="E45" s="3">
+        <v>71700</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>794900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>730200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>880800</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
-        <v>80800</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
+      <c r="M45" s="3">
+        <v>80800</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
-        <v>88400</v>
+      <c r="O45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q45" s="3">
+        <v>88400</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3">
         <v>731200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>719300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>961000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>723800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2028000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1982700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>790300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>323200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>328600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>320000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>402100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>428400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>426500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>346000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>497500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>374100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>345100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>358000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>398300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>375000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>345000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>376000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>381600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>340400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>393600</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4884300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4618300</v>
+      </c>
+      <c r="F46" s="3">
         <v>4888600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5071100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5239800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5275700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5256000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7381400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4813600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4580900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4654500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5045600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5107000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5176400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5116000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5330600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5134000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>5089800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5028600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>6612400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>6320200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>5754500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>6612400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>6408200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5354800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>5121300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4308500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>4478900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>4261400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>4186500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>4169800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>4233800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>4185500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>4123700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>4277100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>4334100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>4338500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>4061400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>4128000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>4111500</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
+      <c r="E47" s="3">
+        <v>254700</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>431900</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
+      <c r="I47" s="3">
+        <v>431900</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>397900</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
+      <c r="M47" s="3">
+        <v>397900</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>462000</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+        <v>462000</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4966,246 +5176,264 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3383400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3828200</v>
+      </c>
+      <c r="F48" s="3">
         <v>3492100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3514400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3583200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4031700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3460500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3457000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3776300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4230000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3643600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3598900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3585200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3976200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3353600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3358000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3358600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3393800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3287900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3291500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>3343200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3606800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>3505500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>3529800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>3557000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>3945800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>3930800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>3992300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>4077600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>3787200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>3822900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>3897400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>3955100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>4047200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>3626200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>3631400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>3648100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>3687700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>3575200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>3571300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20823300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>20839300</v>
+      </c>
+      <c r="F49" s="3">
         <v>22664500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>22624100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>22747500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>22703800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>22577700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>21171000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>21770500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>21730600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>21390900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>21405100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>21487700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>21478800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>21455800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>21450800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>21434000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>21378400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>21557600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>21337100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>21380900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>21213000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>21182900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>21167900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>21160500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>21019000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>21059200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>21106900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>21135000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>21162600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>21221500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>21221000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>21451200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>21510100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>13471400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>13410100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>13425600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>13277600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>13205500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>13166500</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5551,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,127 +5676,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1182400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>476200</v>
+      </c>
+      <c r="F52" s="3">
         <v>1357900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1339400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1445100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>441900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1412000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1386700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1408800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>363000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1171500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1183800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1139800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>358300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1274400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1180400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1180600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1228100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1269700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1240600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1287900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1267600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1348000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1201700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1189900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>720600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>950200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>874300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>839200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>974900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1071600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>1031800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>963000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>943000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>865900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>815900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>797400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>785900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>761600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>752800</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,127 +5926,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30273400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30016700</v>
+      </c>
+      <c r="F54" s="3">
         <v>32403100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>32549000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>33015600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>33071100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>32706200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>33396100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>31769200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>31469900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>30860500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>31233400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>31319700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>31451700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>31199800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>31319800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>31107200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>31090100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>31143800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>32481600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>32332200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>31841900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>32648800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>32307600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>31262200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>30806700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>30248700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>30452400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>30313200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>30111200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>30285800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>30384000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>30554800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>30624000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>22240600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>22191500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>22209600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>21812600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>21670300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>21602100</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +6100,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,722 +6145,760 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3715200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3729500</v>
+      </c>
+      <c r="F57" s="3">
         <v>3634400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3934100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3740000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4009500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3692300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4068800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3823400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3987800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3613500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3824400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3705800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4194200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3868200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4022600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3786300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3982300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3474600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3450000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3288000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3653500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3391600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3398600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3184400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3247700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2931500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3063000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2786700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>2854100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>2750500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>2823900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>2723800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>2746200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>2505700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>2467000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>2172900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>2119800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>1855300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>1938300</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1248400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1224000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2975600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1574600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2188600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2320700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2347700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2085800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1889100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1728100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1498900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2120200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1758900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1842700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3447000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3117700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>3087300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2485600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1325000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1698700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2626000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2825100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>4084400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3011900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2788400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2610500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2038300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2882300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>2687900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>2865200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>3378500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>3046900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>2948600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>3149900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>2461300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>1498500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>2265000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>1838800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>2546700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AQ58" s="3">
         <v>2929300</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1976400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>860700</v>
+      </c>
+      <c r="F59" s="3">
         <v>2075300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2204200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2031000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>539300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1836200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1869700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1576900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>422100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1949500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1957600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1603100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>534800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2103100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2067900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1721900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1552000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2039400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2664500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2221400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1787200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2113700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2053700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1639900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1633300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1726800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1417000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1428800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1367800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1387600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1427300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1515400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>1445800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>1242600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>1384000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>1452000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>1372200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>1341500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>1376800</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6940000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6774100</v>
+      </c>
+      <c r="F60" s="3">
         <v>8685300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7712900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7959600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7857300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7876200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>8024300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7289400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7033100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7061900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7902200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7067800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7535700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>9418300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>9208200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>8595500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>8019900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6839000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>7813200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>8135400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>8265800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>9589700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>8464200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>7612700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>7491500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>6696600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>7362300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>6903400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>7087100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>7516600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>7298100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>7187800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>7341900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>6209600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>5349500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>5889900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>5330800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>5743500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>6244400</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12367200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>12716400</v>
+      </c>
+      <c r="F61" s="3">
         <v>10992100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>12160200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>12218400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>12976000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>11839600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>12435800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11431300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11587000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>11015100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>10530500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>10523500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>10222100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8140200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8622500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>8474600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>9134800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>10944700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>10973600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>10326900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>9786900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>9766600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>10952500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>10832900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>10929000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>11589600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>10953100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>11619800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>11624800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>11642600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>12208600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>12665100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>12668700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>7163600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>8228300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>7822700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>7642900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>7176400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>6542000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1242000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>879800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1239000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1261700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1261800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>925800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1213900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1253900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1326600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1000700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1068700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1142200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1128000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>883000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1006000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3117000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3211500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3147400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3284400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3328500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3300100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3411100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3508600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3450600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3473800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3492100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>3563800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>3571300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>3546600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>3479900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>3328300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>3350300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>3354500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>3344800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>2715200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>3230600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>3246600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>3242500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>3477700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +7016,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6837,8 +7141,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,127 +7266,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22809600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>22636100</v>
+      </c>
+      <c r="F66" s="3">
         <v>23046100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>23220200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>23496700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>23859900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>23193600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>23946900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>22242600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>21821400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>21169200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>21601500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>20804300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>20751700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>20716100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>21198600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>20532400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>20547700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>21330900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>22957100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>22639900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>22371500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>23758500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>23757600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>22817600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>22748200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>22673600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>22740100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>22930400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>23056700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>23355400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>23732200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>24329700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>24482900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>17275000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>17960800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>18305800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>17484700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>17606900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>17421500</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7440,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7561,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7686,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7811,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,127 +7936,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20581400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>20514900</v>
+      </c>
+      <c r="F72" s="3">
         <v>22525400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>22550800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>22791100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>21917800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>21636000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>21340300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>21213900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>20971800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>20416700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>20080900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>20163600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>19838600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>19226500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>18991900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>19027600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>18532600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>17713100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>17363200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>17384500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>17069800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>16655000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>16374200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>16312500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>15982100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>15360000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>15501800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>15218800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>14996700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>14724500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>14572200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>14523800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>14459600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>14398400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>13408900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>13259300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>13138900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>13008800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>12931800</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8186,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8311,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,127 +8436,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7450400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7368400</v>
+      </c>
+      <c r="F76" s="3">
         <v>9343300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9316400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9506600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9199200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9263200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9200700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9275600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9396700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9436800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9378800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>10262400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>10449600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>10234500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>10121200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>10574800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>10542400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>9812900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>9524500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>9692300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>9470400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>8890300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>8550000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>8444600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>8058500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>7575100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>7712300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>7382800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>7054500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>6930400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>6651800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>6225100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>6141100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>4965600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>4230700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>3903800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>4327900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>4063400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>4180600</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,251 +8686,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46264</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="F80" s="2">
         <v>46075</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45984</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45893</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45802</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45711</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45620</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45529</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45438</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45347</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45256</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45165</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45074</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44983</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44892</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44801</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44710</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44619</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44528</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44437</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44346</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44164</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44073</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43982</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43884</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43793</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43702</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43611</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43520</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43429</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43338</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43156</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43065</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42974</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42883</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42792</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42701</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2007900</v>
+      </c>
+      <c r="F81" s="3">
         <v>303100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>413000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1204200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>294000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>625600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>795700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>579900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>557500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>670100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>595500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>673500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>614900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>553100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>605900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>820000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>822800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>660300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>597200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>627000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>416800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>595700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>688400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>638900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>625700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>454100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>580800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>520600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>570200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>446800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>343400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>392300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>354400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>941400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>430500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>404700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>408900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>357800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>481800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,127 +8990,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>138700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>135600</v>
+      </c>
+      <c r="F83" s="3">
         <v>134300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>129500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>139600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>140500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>146400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>128600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>137200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>135600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>137100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>139600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>134300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>139700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>143700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>139600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>134300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>139700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>143700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>141100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>145800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>146800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>159400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>149000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>146100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>138300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>148700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>153600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>154100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>155500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>154500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>154900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>155200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>184100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>143900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>145700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>145100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>155300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>147200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9236,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9361,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9486,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9611,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,127 +9736,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>297800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>552000</v>
+      </c>
+      <c r="F89" s="3">
         <v>397900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>819300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>397000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>611600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>531900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1150500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>624200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>863700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>943100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1117700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>378100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>751600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>826300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>811900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>388800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1088000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>730300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1128000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>369800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>775300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>781100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>843200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>583600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1516400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>703200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>884500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>572100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>779400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>631100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>789100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>607400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>705700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>568500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>976300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>590500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>856500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>480000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,127 +9910,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-90500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-184400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-102400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-143600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-109500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-220200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-103900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-160900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-140300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-288500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-191700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-152200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-141700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-338200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-124600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-135800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-90900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-218100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-126300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-120300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-104000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-184400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-120200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-109200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-117000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-191400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-110900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-88700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-69800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-169700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-114100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-141100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-112700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-224800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-137900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-143700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-116300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-893600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>161400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-329600</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +10156,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,127 +10281,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-174700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-106000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-155900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>1694800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-216300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1272700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-157900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-148000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-689800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-191400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-180700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-135500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-340300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-131200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-140700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>265800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-228900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-65800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-98100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1297900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-180800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-120700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-88300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-181600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-141900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-79000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-83700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-148800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-112300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-155800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-139600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-8260500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-154200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-147900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-122800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-222900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-144000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-152700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,127 +10455,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>330500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>328100</v>
+      </c>
+      <c r="F96" s="3">
         <v>328400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>327900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>330900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>330300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>332600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>338000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>337800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>335400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>337000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>342500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>348500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>320500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>319500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-322900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-325000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-310400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-310900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-310900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-312300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-314000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-314700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-314900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-302800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-300400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-299100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-297800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-298500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-298000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-294500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-295000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-294200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-293200</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-281300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-280900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-284300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-278800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-280800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>-284600</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10701,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10826,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,361 +10951,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-209600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-670600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-210200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-927000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1507200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-570400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1031800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>851500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-429400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-344700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-754000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-839400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-334200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-448500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-725100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-621400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-609100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1105700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-970300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-622200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>195000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1862800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-499100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>19100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-372700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-250100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-511600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-751200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-428600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-718400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-510700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-524300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-423000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>7015200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-438700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-679700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-451300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-662700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-353900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-473200</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-19400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>3300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>5300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>4600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-20500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-28400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>5500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-20500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-28400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>5500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-17000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-18100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>19300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>10100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>12100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>31000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-13800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>1100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>6300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-9200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-10900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-14500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>15400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>38300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>16200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>-29400</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-293800</v>
+      </c>
+      <c r="F102" s="3">
         <v>102100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-269500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>589000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-157400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1771500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1824700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>50100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-170600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>102900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-94600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-33200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>49700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>25000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-275000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-300300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>390700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-751200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1249000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>171400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>786100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>118900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1070900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>46700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>55400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>54800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-97100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>14400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>99800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>33900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-554100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>141300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>54700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-133000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>89400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>44000</v>
       </c>
     </row>
